--- a/public/price-lists/price-list-traders-jun-jul.xlsx
+++ b/public/price-lists/price-list-traders-jun-jul.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מחירון מעוצב" sheetId="1" r:id="R45ef29a1551847ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מחירון מעודכן" sheetId="1" r:id="Rd2e0d5da2dc846bf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,8 +13,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
-    <x:numFmt numFmtId="200" formatCode="#,##0.## &quot;₪&quot;"/>
+  <x:numFmts count="2">
+    <x:numFmt numFmtId="200" formatCode="#,##0 &quot;₪&quot;"/>
+    <x:numFmt numFmtId="201" formatCode="#,##0.## &quot;₪&quot;"/>
   </x:numFmts>
   <x:fonts count="22">
     <x:font>
@@ -138,7 +139,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="14">
+  <x:fills count="15">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -153,6 +154,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF68737D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -206,8 +212,26 @@
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="10">
+  <x:borders count="13">
     <x:border/>
+    <x:border>
+      <x:bottom style="thin">
+        <x:color rgb="FFB9C3CA"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="FFB9C3CA"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFB9C3CA"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="FFB9C3CA"/>
+      </x:top>
+    </x:border>
     <x:border>
       <x:left style="medium">
         <x:color rgb="FF7B878F"/>
@@ -338,7 +362,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="175">
+  <x:cellXfs count="166">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -359,317 +383,466 @@
     <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="right" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="3" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="3" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="3" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="right" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="3" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="3" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="5" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="5" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="5" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="right" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="5" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="5" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="7" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="7" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="7" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="7" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="7" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="right" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="7" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="7" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="7" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="8" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="8" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="8" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="9" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="9" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="9" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="9" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="9" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="10" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="10" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="10" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="10" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="right" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="9" fillId="8" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="8" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="9" fillId="8" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="9" fillId="8" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="9" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="9" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="9" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="11" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="11" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="11" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="11" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="12" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="12" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="12" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="12" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="right" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="11" fillId="9" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="9" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="9" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="11" fillId="9" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="11" fillId="9" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="13" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="13" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="13" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="13" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="13" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="14" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="14" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="14" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="14" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="right" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="13" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="10" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="13" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="13" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="11" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="11" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="11" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="15" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="15" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="15" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="15" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="15" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="16" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="16" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="16" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="16" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="16" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="16" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="right" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="16" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="15" fillId="11" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="11" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="11" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="15" fillId="11" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="15" fillId="11" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="12" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="12" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="12" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="12" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="12" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="17" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="17" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="17" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="17" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="17" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="18" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="18" fillId="12" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="18" fillId="12" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="18" fillId="12" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="12" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="18" fillId="12" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="18" fillId="12" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="right" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="18" fillId="12" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="17" fillId="12" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="12" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="12" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="12" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="17" fillId="12" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="17" fillId="12" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="13" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="13" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="13" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="13" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="12" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="19" fillId="12" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="19" fillId="12" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="19" fillId="12" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="19" fillId="12" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="19" fillId="12" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="20" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="20" fillId="13" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="20" fillId="13" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="20" fillId="13" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="20" fillId="13" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="20" fillId="13" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="right" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="20" fillId="13" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="19" fillId="13" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="13" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="13" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="19" fillId="13" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="19" fillId="13" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="14" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="14" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="14" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="14" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="14" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="14" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="21" fillId="13" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="21" fillId="13" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="21" fillId="13" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="21" fillId="13" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="21" fillId="13" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="12" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="12" fillId="9" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="13" fillId="9" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="21" fillId="14" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="14" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="14" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="14" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="21" fillId="14" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="21" fillId="14" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="10" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="10" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="10" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="10" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="3" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="5" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="7" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="9" fillId="8" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="11" fillId="9" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="13" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="15" fillId="11" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="17" fillId="12" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="19" fillId="13" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="21" fillId="14" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -678,12 +851,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="OriginalPriceList" displayName="OriginalPriceList" ref="A3:C130" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A3:C130"/>
-  <x:tableColumns count="3">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UpdatedPriceList" displayName="UpdatedPriceList" ref="A3:D130" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A3:D130"/>
+  <x:tableColumns count="4">
     <x:tableColumn id="1" name="מק&quot;ט"/>
-    <x:tableColumn id="2" name="תאור מוצר"/>
-    <x:tableColumn id="3" name="מחיר כולל מע&quot;מ"/>
+    <x:tableColumn id="2" name="תיאור מוצר"/>
+    <x:tableColumn id="3" name="קטגוריה"/>
+    <x:tableColumn id="4" name="מחיר כולל מע&quot;מ"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -884,147 +1058,185 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="69" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="54" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
       <x:c r="A1" s="4" t="str">
-        <x:v>מחירון סוחרים כללי 26</x:v>
+        <x:v>מחירון סוחרים יוני יולי</x:v>
       </x:c>
       <x:c r="B1" s="4"/>
       <x:c r="C1" s="4"/>
+      <x:c r="D1" s="4"/>
     </x:row>
     <x:row r="3" ht="25" customHeight="1">
-      <x:c r="A3" s="10" t="str">
+      <x:c r="A3" s="20" t="str">
         <x:v>מק"ט</x:v>
       </x:c>
-      <x:c r="B3" s="11" t="str">
-        <x:v>תאור מוצר</x:v>
-      </x:c>
-      <x:c r="C3" s="12" t="str">
+      <x:c r="B3" s="21" t="str">
+        <x:v>תיאור מוצר</x:v>
+      </x:c>
+      <x:c r="C3" s="21" t="str">
+        <x:v>קטגוריה</x:v>
+      </x:c>
+      <x:c r="D3" s="22" t="str">
         <x:v>מחיר כולל מע"מ</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="20" customHeight="1">
-      <x:c r="A4" s="23" t="str">
+      <x:c r="A4" s="32" t="str">
         <x:v>FJ-32UIL900</x:v>
       </x:c>
-      <x:c r="B4" s="27" t="str">
+      <x:c r="B4" s="34" t="str">
         <x:v>FUJICOM 32" SMART TV FJ-32UIL900</x:v>
       </x:c>
-      <x:c r="C4" s="33" t="n">
+      <x:c r="C4" s="36" t="str">
+        <x:v>טלוויזיות</x:v>
+      </x:c>
+      <x:c r="D4" s="156" t="n">
         <x:v>475</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="20" customHeight="1">
-      <x:c r="A5" s="23" t="str">
+      <x:c r="A5" s="32" t="str">
         <x:v>FJ-43UIL900</x:v>
       </x:c>
-      <x:c r="B5" s="27" t="str">
+      <x:c r="B5" s="34" t="str">
         <x:v>FUJICOM FRAMELESS  43"  FJ-43UIL900  SMART WEBOS TV</x:v>
       </x:c>
-      <x:c r="C5" s="33" t="n">
+      <x:c r="C5" s="36" t="str">
+        <x:v>טלוויזיות</x:v>
+      </x:c>
+      <x:c r="D5" s="156" t="n">
         <x:v>750</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="20" customHeight="1">
-      <x:c r="A6" s="23" t="str">
+      <x:c r="A6" s="32" t="str">
         <x:v>FJ-50UILQ950</x:v>
       </x:c>
-      <x:c r="B6" s="27" t="str">
+      <x:c r="B6" s="34" t="str">
         <x:v>FUJICOM 50"  QLED FJ-50UILQ950  SMART TV</x:v>
       </x:c>
-      <x:c r="C6" s="33" t="n">
+      <x:c r="C6" s="36" t="str">
+        <x:v>טלוויזיות</x:v>
+      </x:c>
+      <x:c r="D6" s="156" t="n">
         <x:v>975</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="20" customHeight="1">
-      <x:c r="A7" s="23" t="str">
+      <x:c r="A7" s="32" t="str">
         <x:v>FJ-55UILQ950</x:v>
       </x:c>
-      <x:c r="B7" s="27" t="str">
+      <x:c r="B7" s="34" t="str">
         <x:v>55" QLED FUJICOM   SMART  TV FJ-55UILQ950</x:v>
       </x:c>
-      <x:c r="C7" s="33" t="n">
+      <x:c r="C7" s="36" t="str">
+        <x:v>טלוויזיות</x:v>
+      </x:c>
+      <x:c r="D7" s="156" t="n">
         <x:v>1125</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="20" customHeight="1">
-      <x:c r="A8" s="23" t="str">
+      <x:c r="A8" s="32" t="str">
         <x:v>FJ-65Q10X</x:v>
       </x:c>
-      <x:c r="B8" s="27" t="str">
+      <x:c r="B8" s="34" t="str">
         <x:v>FUJICOM FRAMELESS  65"  QLED  FJ-65Q10X  SMART WEBOS TV</x:v>
       </x:c>
-      <x:c r="C8" s="33" t="n">
+      <x:c r="C8" s="36" t="str">
+        <x:v>טלוויזיות</x:v>
+      </x:c>
+      <x:c r="D8" s="156" t="n">
         <x:v>1550</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="20" customHeight="1">
-      <x:c r="A9" s="23" t="str">
+      <x:c r="A9" s="32" t="str">
         <x:v>FJ-75UILQ950</x:v>
       </x:c>
-      <x:c r="B9" s="27" t="str">
+      <x:c r="B9" s="34" t="str">
         <x:v>FUJICOM  75"  QLED FJ-75UILQ950  SMART  TV</x:v>
       </x:c>
-      <x:c r="C9" s="33" t="n">
+      <x:c r="C9" s="36" t="str">
+        <x:v>טלוויזיות</x:v>
+      </x:c>
+      <x:c r="D9" s="156" t="n">
         <x:v>2150</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="20" customHeight="1">
-      <x:c r="A10" s="38" t="str">
+      <x:c r="A10" s="44" t="str">
         <x:v>FJ-MW20LW</x:v>
       </x:c>
-      <x:c r="B10" s="42" t="str">
+      <x:c r="B10" s="46" t="str">
         <x:v>מיקרוגל  מכני 20 ליטר לבן  FJ-MW20LW</x:v>
       </x:c>
-      <x:c r="C10" s="48" t="n">
+      <x:c r="C10" s="48" t="str">
+        <x:v>מיקרוגלים</x:v>
+      </x:c>
+      <x:c r="D10" s="157" t="n">
         <x:v>252.14</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="20" customHeight="1">
-      <x:c r="A11" s="38" t="str">
+      <x:c r="A11" s="44" t="str">
         <x:v>FJ-MW25LB</x:v>
       </x:c>
-      <x:c r="B11" s="42" t="str">
+      <x:c r="B11" s="46" t="str">
         <x:v>מיקרוגל דיגיטלי 25 ליטר שחור FJ-MW25LB</x:v>
       </x:c>
-      <x:c r="C11" s="48" t="n">
+      <x:c r="C11" s="48" t="str">
+        <x:v>מיקרוגלים</x:v>
+      </x:c>
+      <x:c r="D11" s="157" t="n">
         <x:v>352.99</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="20" customHeight="1">
-      <x:c r="A12" s="53" t="str">
+      <x:c r="A12" s="56" t="str">
         <x:v>FJ-B957E</x:v>
       </x:c>
-      <x:c r="B12" s="57" t="str">
+      <x:c r="B12" s="58" t="str">
         <x:v>מקרר אנטגרלי 294 ליטר</x:v>
       </x:c>
-      <x:c r="C12" s="63" t="n">
+      <x:c r="C12" s="60" t="str">
+        <x:v>קירור אינטגרלי</x:v>
+      </x:c>
+      <x:c r="D12" s="158" t="n">
         <x:v>2190</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="20" customHeight="1">
-      <x:c r="A13" s="53" t="str">
+      <x:c r="A13" s="56" t="str">
         <x:v>FJ-BFNF927E</x:v>
       </x:c>
-      <x:c r="B13" s="57" t="str">
+      <x:c r="B13" s="58" t="str">
         <x:v>מקפיא אינטגרלי 197 ליטר NF</x:v>
       </x:c>
-      <x:c r="C13" s="63" t="n">
+      <x:c r="C13" s="60" t="str">
+        <x:v>קירור אינטגרלי</x:v>
+      </x:c>
+      <x:c r="D13" s="158" t="n">
         <x:v>2190</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="20" customHeight="1">
-      <x:c r="A14" s="53" t="str">
+      <x:c r="A14" s="56" t="str">
         <x:v>FJ-BINF410</x:v>
       </x:c>
-      <x:c r="B14" s="57" t="str">
+      <x:c r="B14" s="58" t="str">
         <x:v>מקרר  אינטגרלי מקפיא תחתון 70 ס"מ 403 ליטר NF</x:v>
       </x:c>
-      <x:c r="C14" s="63" t="n">
+      <x:c r="C14" s="60" t="str">
+        <x:v>קירור אינטגרלי</x:v>
+      </x:c>
+      <x:c r="D14" s="158" t="n">
         <x:v>3590</x:v>
       </x:c>
     </x:row>
@@ -1032,10 +1244,13 @@
       <x:c r="A15" s="68" t="str">
         <x:v>FJ-BIOV980</x:v>
       </x:c>
-      <x:c r="B15" s="72" t="str">
+      <x:c r="B15" s="70" t="str">
         <x:v>תנור בנוי מכני 73 ליטר שחור</x:v>
       </x:c>
-      <x:c r="C15" s="78" t="n">
+      <x:c r="C15" s="72" t="str">
+        <x:v>תנורים</x:v>
+      </x:c>
+      <x:c r="D15" s="159" t="n">
         <x:v>690</x:v>
       </x:c>
     </x:row>
@@ -1043,10 +1258,13 @@
       <x:c r="A16" s="68" t="str">
         <x:v>FJ-BIOV990W</x:v>
       </x:c>
-      <x:c r="B16" s="72" t="str">
+      <x:c r="B16" s="70" t="str">
         <x:v>תנור בנוי מכני 73 ליטר לבן</x:v>
       </x:c>
-      <x:c r="C16" s="78" t="n">
+      <x:c r="C16" s="72" t="str">
+        <x:v>תנורים</x:v>
+      </x:c>
+      <x:c r="D16" s="159" t="n">
         <x:v>690</x:v>
       </x:c>
     </x:row>
@@ -1054,10 +1272,13 @@
       <x:c r="A17" s="68" t="str">
         <x:v>FJ-BIOVRT90W</x:v>
       </x:c>
-      <x:c r="B17" s="72" t="str">
+      <x:c r="B17" s="70" t="str">
         <x:v>תנור בנוי כפרי  רטרו  73 ליטר צבע שמנת</x:v>
       </x:c>
-      <x:c r="C17" s="78" t="n">
+      <x:c r="C17" s="72" t="str">
+        <x:v>תנורים</x:v>
+      </x:c>
+      <x:c r="D17" s="159" t="n">
         <x:v>1145</x:v>
       </x:c>
     </x:row>
@@ -1065,10 +1286,13 @@
       <x:c r="A18" s="68" t="str">
         <x:v>FJ-BIRT8B</x:v>
       </x:c>
-      <x:c r="B18" s="72" t="str">
+      <x:c r="B18" s="70" t="str">
         <x:v>תנור בנוי כפרי 80 ליטר שמנת</x:v>
       </x:c>
-      <x:c r="C18" s="78" t="n">
+      <x:c r="C18" s="72" t="str">
+        <x:v>תנורים</x:v>
+      </x:c>
+      <x:c r="D18" s="159" t="n">
         <x:v>1145</x:v>
       </x:c>
     </x:row>
@@ -1076,10 +1300,13 @@
       <x:c r="A19" s="68" t="str">
         <x:v>FJ-BIRT9CK</x:v>
       </x:c>
-      <x:c r="B19" s="72" t="str">
+      <x:c r="B19" s="70" t="str">
         <x:v>תנור בנוי כפרי 80 ליטר שחור מט</x:v>
       </x:c>
-      <x:c r="C19" s="78" t="n">
+      <x:c r="C19" s="72" t="str">
+        <x:v>תנורים</x:v>
+      </x:c>
+      <x:c r="D19" s="159" t="n">
         <x:v>1145</x:v>
       </x:c>
     </x:row>
@@ -1087,10 +1314,13 @@
       <x:c r="A20" s="68" t="str">
         <x:v>FJ-BO770T</x:v>
       </x:c>
-      <x:c r="B20" s="72" t="str">
+      <x:c r="B20" s="70" t="str">
         <x:v>תנור בנוי 72 ליטר מסך מגע שחור</x:v>
       </x:c>
-      <x:c r="C20" s="78" t="n">
+      <x:c r="C20" s="72" t="str">
+        <x:v>תנורים</x:v>
+      </x:c>
+      <x:c r="D20" s="159" t="n">
         <x:v>1250</x:v>
       </x:c>
     </x:row>
@@ -1098,10 +1328,13 @@
       <x:c r="A21" s="68" t="str">
         <x:v>FJ-BO797BL</x:v>
       </x:c>
-      <x:c r="B21" s="72" t="str">
+      <x:c r="B21" s="70" t="str">
         <x:v>תנור בנוי דיגטלי 70 ליטר שחור</x:v>
       </x:c>
-      <x:c r="C21" s="78" t="n">
+      <x:c r="C21" s="72" t="str">
+        <x:v>תנורים</x:v>
+      </x:c>
+      <x:c r="D21" s="159" t="n">
         <x:v>1150</x:v>
       </x:c>
     </x:row>
@@ -1109,373 +1342,475 @@
       <x:c r="A22" s="68" t="str">
         <x:v>FJ-BOMW245BL</x:v>
       </x:c>
-      <x:c r="B22" s="72" t="str">
+      <x:c r="B22" s="70" t="str">
         <x:v>תנור בנוי  44 ליטר משולב מיקרו 45 ס"מ שחור</x:v>
       </x:c>
-      <x:c r="C22" s="78" t="n">
+      <x:c r="C22" s="72" t="str">
+        <x:v>תנורים</x:v>
+      </x:c>
+      <x:c r="D22" s="159" t="n">
         <x:v>1800</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="20" customHeight="1">
-      <x:c r="A23" s="83" t="str">
+      <x:c r="A23" s="80" t="str">
         <x:v>FJ-CHRT60B</x:v>
       </x:c>
-      <x:c r="B23" s="87" t="str">
+      <x:c r="B23" s="82" t="str">
         <x:v>קולט אדים 60 ס"מ  שמנת  כפרי</x:v>
       </x:c>
-      <x:c r="C23" s="93" t="n">
+      <x:c r="C23" s="84" t="str">
+        <x:v>קולטי אדים</x:v>
+      </x:c>
+      <x:c r="D23" s="160" t="n">
         <x:v>680</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="20" customHeight="1">
-      <x:c r="A24" s="83" t="str">
+      <x:c r="A24" s="80" t="str">
         <x:v>FJ-CHRT70CK</x:v>
       </x:c>
-      <x:c r="B24" s="87" t="str">
+      <x:c r="B24" s="82" t="str">
         <x:v>קולט אדים 60 ס"מ  שחור מט כפרי</x:v>
       </x:c>
-      <x:c r="C24" s="93" t="n">
+      <x:c r="C24" s="84" t="str">
+        <x:v>קולטי אדים</x:v>
+      </x:c>
+      <x:c r="D24" s="160" t="n">
         <x:v>680</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="20" customHeight="1">
-      <x:c r="A25" s="83" t="str">
+      <x:c r="A25" s="80" t="str">
         <x:v>FJ-CHRT91B</x:v>
       </x:c>
-      <x:c r="B25" s="87" t="str">
+      <x:c r="B25" s="82" t="str">
         <x:v>קולט אדים 90 ס"מ  שמנת  כפרי</x:v>
       </x:c>
-      <x:c r="C25" s="93" t="n">
+      <x:c r="C25" s="84" t="str">
+        <x:v>קולטי אדים</x:v>
+      </x:c>
+      <x:c r="D25" s="160" t="n">
         <x:v>899</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="20" customHeight="1">
-      <x:c r="A26" s="83" t="str">
+      <x:c r="A26" s="80" t="str">
         <x:v>FJ-CHRT92CK</x:v>
       </x:c>
-      <x:c r="B26" s="87" t="str">
+      <x:c r="B26" s="82" t="str">
         <x:v>קולט אדים 90 ס"מ ע שחור מט  כפרי</x:v>
       </x:c>
-      <x:c r="C26" s="93" t="n">
+      <x:c r="C26" s="84" t="str">
+        <x:v>קולטי אדים</x:v>
+      </x:c>
+      <x:c r="D26" s="160" t="n">
         <x:v>899</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="20" customHeight="1">
-      <x:c r="A27" s="83" t="str">
+      <x:c r="A27" s="80" t="str">
         <x:v>FJ-CHT11BL</x:v>
       </x:c>
-      <x:c r="B27" s="87" t="str">
+      <x:c r="B27" s="82" t="str">
         <x:v>קולט  אדים מרובע 60 ס"מ זכוכית שחורה</x:v>
       </x:c>
-      <x:c r="C27" s="93" t="n">
+      <x:c r="C27" s="84" t="str">
+        <x:v>קולטי אדים</x:v>
+      </x:c>
+      <x:c r="D27" s="160" t="n">
         <x:v>595</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="20" customHeight="1">
-      <x:c r="A28" s="83" t="str">
+      <x:c r="A28" s="80" t="str">
         <x:v>FJ-CHT13W</x:v>
       </x:c>
-      <x:c r="B28" s="87" t="str">
+      <x:c r="B28" s="82" t="str">
         <x:v>קולט אדים מרובע 60 ס"מ זכוכית לבנה</x:v>
       </x:c>
-      <x:c r="C28" s="93" t="n">
+      <x:c r="C28" s="84" t="str">
+        <x:v>קולטי אדים</x:v>
+      </x:c>
+      <x:c r="D28" s="160" t="n">
         <x:v>595</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="20" customHeight="1">
-      <x:c r="A29" s="83" t="str">
+      <x:c r="A29" s="80" t="str">
         <x:v>FJ-CHT50W</x:v>
       </x:c>
-      <x:c r="B29" s="87" t="str">
+      <x:c r="B29" s="82" t="str">
         <x:v>קולט  אדים זכוכית כפולה 60 ס"מ  זכוכית לבנה</x:v>
       </x:c>
-      <x:c r="C29" s="93" t="n">
+      <x:c r="C29" s="84" t="str">
+        <x:v>קולטי אדים</x:v>
+      </x:c>
+      <x:c r="D29" s="160" t="n">
         <x:v>595</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="20" customHeight="1">
-      <x:c r="A30" s="83" t="str">
+      <x:c r="A30" s="80" t="str">
         <x:v>FJ-CHT60BL</x:v>
       </x:c>
-      <x:c r="B30" s="87" t="str">
+      <x:c r="B30" s="82" t="str">
         <x:v>קולט אדים זכוכית כפולה 60 ס"מ זכוכית שחורה</x:v>
       </x:c>
-      <x:c r="C30" s="93" t="n">
+      <x:c r="C30" s="84" t="str">
+        <x:v>קולטי אדים</x:v>
+      </x:c>
+      <x:c r="D30" s="160" t="n">
         <x:v>595</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="20" customHeight="1">
-      <x:c r="A31" s="83" t="str">
+      <x:c r="A31" s="80" t="str">
         <x:v>FJ-CHT74W</x:v>
       </x:c>
-      <x:c r="B31" s="87" t="str">
+      <x:c r="B31" s="82" t="str">
         <x:v>קולט אדים זכוכית כפולה 90 ס"מ זכוכית לבנה</x:v>
       </x:c>
-      <x:c r="C31" s="93" t="n">
+      <x:c r="C31" s="84" t="str">
+        <x:v>קולטי אדים</x:v>
+      </x:c>
+      <x:c r="D31" s="160" t="n">
         <x:v>695</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="20" customHeight="1">
-      <x:c r="A32" s="83" t="str">
+      <x:c r="A32" s="80" t="str">
         <x:v>FJ-CHT90BL</x:v>
       </x:c>
-      <x:c r="B32" s="87" t="str">
+      <x:c r="B32" s="82" t="str">
         <x:v>קולט אדים זכוכית כפולה 90 ס"מ  זכוכית שחורה</x:v>
       </x:c>
-      <x:c r="C32" s="93" t="n">
+      <x:c r="C32" s="84" t="str">
+        <x:v>קולטי אדים</x:v>
+      </x:c>
+      <x:c r="D32" s="160" t="n">
         <x:v>695</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="20" customHeight="1">
-      <x:c r="A33" s="98" t="str">
+      <x:c r="A33" s="92" t="str">
         <x:v>FJ-DF117WE</x:v>
       </x:c>
-      <x:c r="B33" s="102" t="str">
+      <x:c r="B33" s="94" t="str">
         <x:v>מקרר משרדי 86 ל'  לבן</x:v>
       </x:c>
-      <x:c r="C33" s="108" t="n">
+      <x:c r="C33" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D33" s="161" t="n">
         <x:v>390</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="20" customHeight="1">
-      <x:c r="A34" s="98" t="str">
+      <x:c r="A34" s="92" t="str">
         <x:v>FJ-DF177S</x:v>
       </x:c>
-      <x:c r="B34" s="102" t="str">
+      <x:c r="B34" s="94" t="str">
         <x:v>מקרר משרדי  DE-FROST  כסוף 86 ליטר</x:v>
       </x:c>
-      <x:c r="C34" s="108" t="n">
+      <x:c r="C34" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D34" s="161" t="n">
         <x:v>410</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="20" customHeight="1">
-      <x:c r="A35" s="98" t="str">
+      <x:c r="A35" s="92" t="str">
         <x:v>FJ-DF28WE</x:v>
       </x:c>
-      <x:c r="B35" s="102" t="str">
+      <x:c r="B35" s="94" t="str">
         <x:v>מקרר מקפיא עליון 206 ליטר DF  לבן</x:v>
       </x:c>
-      <x:c r="C35" s="108" t="n">
+      <x:c r="C35" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D35" s="161" t="n">
         <x:v>700</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="20" customHeight="1">
-      <x:c r="A36" s="98" t="str">
+      <x:c r="A36" s="92" t="str">
         <x:v>FJ-DF300W</x:v>
       </x:c>
-      <x:c r="B36" s="102" t="str">
+      <x:c r="B36" s="94" t="str">
         <x:v>מקפיא/מקרר שוכב תעשייתי  293 ליטר לבן</x:v>
       </x:c>
-      <x:c r="C36" s="108" t="n">
+      <x:c r="C36" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D36" s="161" t="n">
         <x:v>990</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="20" customHeight="1">
-      <x:c r="A37" s="98" t="str">
+      <x:c r="A37" s="92" t="str">
         <x:v>FJ-DF35XE</x:v>
       </x:c>
-      <x:c r="B37" s="102" t="str">
+      <x:c r="B37" s="94" t="str">
         <x:v>מקרר מקפיא עליון 206 ליטר DF כסוף</x:v>
       </x:c>
-      <x:c r="C37" s="108" t="n">
+      <x:c r="C37" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D37" s="161" t="n">
         <x:v>700</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="20" customHeight="1">
-      <x:c r="A38" s="98" t="str">
+      <x:c r="A38" s="92" t="str">
         <x:v>FJ-DF400W</x:v>
       </x:c>
-      <x:c r="B38" s="102" t="str">
+      <x:c r="B38" s="94" t="str">
         <x:v>מקפיא תעשייתי שוכב  DE-FROST  392 ליטר לבן</x:v>
       </x:c>
-      <x:c r="C38" s="108" t="n">
+      <x:c r="C38" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D38" s="161" t="n">
         <x:v>1190</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="20" customHeight="1">
-      <x:c r="A39" s="98" t="str">
+      <x:c r="A39" s="92" t="str">
         <x:v>FJ-DF46L</x:v>
       </x:c>
-      <x:c r="B39" s="102" t="str">
+      <x:c r="B39" s="94" t="str">
         <x:v>מקרר קוביה  46 ליטר  לבן</x:v>
       </x:c>
-      <x:c r="C39" s="108" t="n">
+      <x:c r="C39" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D39" s="161" t="n">
         <x:v>375</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="20" customHeight="1">
-      <x:c r="A40" s="113" t="str">
+      <x:c r="A40" s="104" t="str">
         <x:v>FJ-DHP909</x:v>
       </x:c>
-      <x:c r="B40" s="117" t="str">
+      <x:c r="B40" s="106" t="str">
         <x:v>מייבש כביסה 9 ק"ג Heat Pump</x:v>
       </x:c>
-      <x:c r="C40" s="123" t="n">
+      <x:c r="C40" s="108" t="str">
+        <x:v>מייבשים</x:v>
+      </x:c>
+      <x:c r="D40" s="162" t="n">
         <x:v>1800</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="20" customHeight="1">
-      <x:c r="A41" s="128" t="str">
+      <x:c r="A41" s="116" t="str">
         <x:v>FJ-DW20W</x:v>
       </x:c>
-      <x:c r="B41" s="132" t="str">
+      <x:c r="B41" s="118" t="str">
         <x:v>מדיח כלים 8 תוכניות  לבן</x:v>
       </x:c>
-      <x:c r="C41" s="138" t="n">
+      <x:c r="C41" s="120" t="str">
+        <x:v>מדיחים</x:v>
+      </x:c>
+      <x:c r="D41" s="163" t="n">
         <x:v>950</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="20" customHeight="1">
-      <x:c r="A42" s="128" t="str">
+      <x:c r="A42" s="116" t="str">
         <x:v>FJ-DW22X</x:v>
       </x:c>
-      <x:c r="B42" s="132" t="str">
+      <x:c r="B42" s="118" t="str">
         <x:v>מדיח כלים 8 תוכניות  נירוסטה</x:v>
       </x:c>
-      <x:c r="C42" s="138" t="n">
+      <x:c r="C42" s="120" t="str">
+        <x:v>מדיחים</x:v>
+      </x:c>
+      <x:c r="D42" s="163" t="n">
         <x:v>1090</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="20" customHeight="1">
-      <x:c r="A43" s="128" t="str">
+      <x:c r="A43" s="116" t="str">
         <x:v>FJ-DW24BK</x:v>
       </x:c>
-      <x:c r="B43" s="132" t="str">
+      <x:c r="B43" s="118" t="str">
         <x:v>מדיח כלים 8 תוכניות  שחור</x:v>
       </x:c>
-      <x:c r="C43" s="138" t="n">
+      <x:c r="C43" s="120" t="str">
+        <x:v>מדיחים</x:v>
+      </x:c>
+      <x:c r="D43" s="163" t="n">
         <x:v>1150</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="20" customHeight="1">
-      <x:c r="A44" s="128" t="str">
+      <x:c r="A44" s="116" t="str">
         <x:v>FJ-DW6T</x:v>
       </x:c>
-      <x:c r="B44" s="132" t="str">
+      <x:c r="B44" s="118" t="str">
         <x:v>מדיח כלים על השיש 7 תוכניות  לבן</x:v>
       </x:c>
-      <x:c r="C44" s="138" t="n">
+      <x:c r="C44" s="120" t="str">
+        <x:v>מדיחים</x:v>
+      </x:c>
+      <x:c r="D44" s="163" t="n">
         <x:v>690</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="20" customHeight="1">
-      <x:c r="A45" s="128" t="str">
+      <x:c r="A45" s="116" t="str">
         <x:v>FJ-DWB8817</x:v>
       </x:c>
-      <x:c r="B45" s="132" t="str">
+      <x:c r="B45" s="118" t="str">
         <x:v>מדיח כלים אינטגרלי מלא</x:v>
       </x:c>
-      <x:c r="C45" s="138" t="n">
+      <x:c r="C45" s="120" t="str">
+        <x:v>מדיחים</x:v>
+      </x:c>
+      <x:c r="D45" s="163" t="n">
         <x:v>1290</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="20" customHeight="1">
-      <x:c r="A46" s="128" t="str">
+      <x:c r="A46" s="116" t="str">
         <x:v>FJ-DWIGBK</x:v>
       </x:c>
-      <x:c r="B46" s="132" t="str">
+      <x:c r="B46" s="118" t="str">
         <x:v>מדיח כלים 14 מערכות דלת זכוכית שחור FJ-DWIGBK</x:v>
       </x:c>
-      <x:c r="C46" s="138" t="n">
+      <x:c r="C46" s="120" t="str">
+        <x:v>מדיחים</x:v>
+      </x:c>
+      <x:c r="D46" s="163" t="n">
         <x:v>1190</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="20" customHeight="1">
-      <x:c r="A47" s="98" t="str">
+      <x:c r="A47" s="92" t="str">
         <x:v>FJ-FDF155W</x:v>
       </x:c>
-      <x:c r="B47" s="102" t="str">
+      <x:c r="B47" s="94" t="str">
         <x:v>מקפיא  4  מגירות 91 ליטר DE FROST  לבן</x:v>
       </x:c>
-      <x:c r="C47" s="108" t="n">
+      <x:c r="C47" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D47" s="161" t="n">
         <x:v>650</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="20" customHeight="1">
-      <x:c r="A48" s="53" t="str">
+      <x:c r="A48" s="56" t="str">
         <x:v>FJ-FNF212BI</x:v>
       </x:c>
-      <x:c r="B48" s="57" t="str">
+      <x:c r="B48" s="58" t="str">
         <x:v>מקפיא אינטגרלי 212 ליטר  NO-FROST</x:v>
       </x:c>
-      <x:c r="C48" s="63" t="n">
+      <x:c r="C48" s="60" t="str">
+        <x:v>קירור אינטגרלי</x:v>
+      </x:c>
+      <x:c r="D48" s="158" t="n">
         <x:v>2190</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="20" customHeight="1">
-      <x:c r="A49" s="98" t="str">
+      <x:c r="A49" s="92" t="str">
         <x:v>FJ-FNF226W</x:v>
       </x:c>
-      <x:c r="B49" s="102" t="str">
+      <x:c r="B49" s="94" t="str">
         <x:v>מקפיא 6 מגירות 213 ליטר NO-FROST לבן</x:v>
       </x:c>
-      <x:c r="C49" s="108" t="n">
+      <x:c r="C49" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D49" s="161" t="n">
         <x:v>1190</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="20" customHeight="1">
-      <x:c r="A50" s="98" t="str">
+      <x:c r="A50" s="92" t="str">
         <x:v>FJ-FNF377WE</x:v>
       </x:c>
-      <x:c r="B50" s="102" t="str">
+      <x:c r="B50" s="94" t="str">
         <x:v>מקפיא 7 מגירות 280 ליטר NF  לבן</x:v>
       </x:c>
-      <x:c r="C50" s="108" t="n">
+      <x:c r="C50" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D50" s="161" t="n">
         <x:v>1675</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="20" customHeight="1">
-      <x:c r="A51" s="98" t="str">
+      <x:c r="A51" s="92" t="str">
         <x:v>FJ-FNF488W</x:v>
       </x:c>
-      <x:c r="B51" s="102" t="str">
+      <x:c r="B51" s="94" t="str">
         <x:v>מקפיא 8 תאים 273 ליטר NO FROST  לבן</x:v>
       </x:c>
-      <x:c r="C51" s="108" t="n">
+      <x:c r="C51" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D51" s="161" t="n">
         <x:v>1550</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="20" customHeight="1">
-      <x:c r="A52" s="98" t="str">
+      <x:c r="A52" s="92" t="str">
         <x:v>FJ-FNF588X</x:v>
       </x:c>
-      <x:c r="B52" s="102" t="str">
+      <x:c r="B52" s="94" t="str">
         <x:v>מקפיא 8 תאים 273 ליטר NO FROST  נירוסטה</x:v>
       </x:c>
-      <x:c r="C52" s="108" t="n">
+      <x:c r="C52" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D52" s="161" t="n">
         <x:v>1650</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="20" customHeight="1">
-      <x:c r="A53" s="143" t="str">
+      <x:c r="A53" s="128" t="str">
         <x:v>FJ-FS6365W</x:v>
       </x:c>
-      <x:c r="B53" s="147" t="str">
+      <x:c r="B53" s="130" t="str">
         <x:v>תנור עומד משולב 60 ליטר כולל כיריים גז לבן</x:v>
       </x:c>
-      <x:c r="C53" s="153" t="n">
+      <x:c r="C53" s="132" t="str">
+        <x:v>כיריים</x:v>
+      </x:c>
+      <x:c r="D53" s="164" t="n">
         <x:v>1090</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="20" customHeight="1">
-      <x:c r="A54" s="143" t="str">
+      <x:c r="A54" s="128" t="str">
         <x:v>FJ-FS8065X</x:v>
       </x:c>
-      <x:c r="B54" s="147" t="str">
+      <x:c r="B54" s="130" t="str">
         <x:v>תנור עומד משולב 60 ליטר כולל כיריים גז  נירוסטה</x:v>
       </x:c>
-      <x:c r="C54" s="153" t="n">
+      <x:c r="C54" s="132" t="str">
+        <x:v>כיריים</x:v>
+      </x:c>
+      <x:c r="D54" s="164" t="n">
         <x:v>1245</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="20" customHeight="1">
-      <x:c r="A55" s="143" t="str">
+      <x:c r="A55" s="128" t="str">
         <x:v>FJ-FSC75BK</x:v>
       </x:c>
-      <x:c r="B55" s="147" t="str">
+      <x:c r="B55" s="130" t="str">
         <x:v>תנור עומד משולב 60 ליטר כולל כיריים גז שחור</x:v>
       </x:c>
-      <x:c r="C55" s="153" t="n">
+      <x:c r="C55" s="132" t="str">
+        <x:v>כיריים</x:v>
+      </x:c>
+      <x:c r="D55" s="164" t="n">
         <x:v>1185</x:v>
       </x:c>
     </x:row>
@@ -1483,10 +1818,13 @@
       <x:c r="A56" s="68" t="str">
         <x:v>FJ-FSC9060B</x:v>
       </x:c>
-      <x:c r="B56" s="72" t="str">
+      <x:c r="B56" s="70" t="str">
         <x:v>תנור משולב 90 ס"מ כפרי מכסה עליון נירוסטה  5 מבערים  שמנת</x:v>
       </x:c>
-      <x:c r="C56" s="78" t="n">
+      <x:c r="C56" s="72" t="str">
+        <x:v>תנורים</x:v>
+      </x:c>
+      <x:c r="D56" s="159" t="n">
         <x:v>2890</x:v>
       </x:c>
     </x:row>
@@ -1494,823 +1832,1045 @@
       <x:c r="A57" s="68" t="str">
         <x:v>FJ-FSC9095BK</x:v>
       </x:c>
-      <x:c r="B57" s="72" t="str">
+      <x:c r="B57" s="70" t="str">
         <x:v>תנור משולב 90 ס"מ כפרי מכסה עליון נירוסטה  5 מבערים שחור מט</x:v>
       </x:c>
-      <x:c r="C57" s="78" t="n">
+      <x:c r="C57" s="72" t="str">
+        <x:v>תנורים</x:v>
+      </x:c>
+      <x:c r="D57" s="159" t="n">
         <x:v>2890</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="20" customHeight="1">
-      <x:c r="A58" s="143" t="str">
+      <x:c r="A58" s="128" t="str">
         <x:v>FJ-FSRT60BG</x:v>
       </x:c>
-      <x:c r="B58" s="147" t="str">
+      <x:c r="B58" s="130" t="str">
         <x:v>תנור עומד  רטרו 60 ס"מ בצבע שמנת כולל כיריים</x:v>
       </x:c>
-      <x:c r="C58" s="153" t="n">
+      <x:c r="C58" s="132" t="str">
+        <x:v>כיריים</x:v>
+      </x:c>
+      <x:c r="D58" s="164" t="n">
         <x:v>1490</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="20" customHeight="1">
-      <x:c r="A59" s="143" t="str">
+      <x:c r="A59" s="128" t="str">
         <x:v>FJ-FSRT66MB</x:v>
       </x:c>
-      <x:c r="B59" s="147" t="str">
+      <x:c r="B59" s="130" t="str">
         <x:v>תנור עומד  רטרו 60 ס"מ צבע שחור מט כולל כיריים</x:v>
       </x:c>
-      <x:c r="C59" s="153" t="n">
+      <x:c r="C59" s="132" t="str">
+        <x:v>כיריים</x:v>
+      </x:c>
+      <x:c r="D59" s="164" t="n">
         <x:v>1490</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="20" customHeight="1">
-      <x:c r="A60" s="143" t="str">
+      <x:c r="A60" s="128" t="str">
         <x:v>FJ-GH755W</x:v>
       </x:c>
-      <x:c r="B60" s="147" t="str">
+      <x:c r="B60" s="130" t="str">
         <x:v>כיריים גז 4 מבערים זכוכית לבנה</x:v>
       </x:c>
-      <x:c r="C60" s="153" t="n">
+      <x:c r="C60" s="132" t="str">
+        <x:v>כיריים</x:v>
+      </x:c>
+      <x:c r="D60" s="164" t="n">
         <x:v>579</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="20" customHeight="1">
-      <x:c r="A61" s="143" t="str">
+      <x:c r="A61" s="128" t="str">
         <x:v>FJ-GH840BK</x:v>
       </x:c>
-      <x:c r="B61" s="147" t="str">
+      <x:c r="B61" s="130" t="str">
         <x:v>כיריים גז 4 מבערים - זכוכית שחורה</x:v>
       </x:c>
-      <x:c r="C61" s="153" t="n">
+      <x:c r="C61" s="132" t="str">
+        <x:v>כיריים</x:v>
+      </x:c>
+      <x:c r="D61" s="164" t="n">
         <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="20" customHeight="1">
-      <x:c r="A62" s="143" t="str">
+      <x:c r="A62" s="128" t="str">
         <x:v>FJ-GH950W</x:v>
       </x:c>
-      <x:c r="B62" s="147" t="str">
+      <x:c r="B62" s="130" t="str">
         <x:v>כיריים גז 4 מבערים - זכוכית לבנה</x:v>
       </x:c>
-      <x:c r="C62" s="153" t="n">
+      <x:c r="C62" s="132" t="str">
+        <x:v>כיריים</x:v>
+      </x:c>
+      <x:c r="D62" s="164" t="n">
         <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="20" customHeight="1">
-      <x:c r="A63" s="143" t="str">
+      <x:c r="A63" s="128" t="str">
         <x:v>FJ-GHRT13BG</x:v>
       </x:c>
-      <x:c r="B63" s="147" t="str">
+      <x:c r="B63" s="130" t="str">
         <x:v>כיריים גז 4 מבערים כפרי רטרו  צבע שמנת</x:v>
       </x:c>
-      <x:c r="C63" s="153" t="n">
+      <x:c r="C63" s="132" t="str">
+        <x:v>כיריים</x:v>
+      </x:c>
+      <x:c r="D63" s="164" t="n">
         <x:v>620</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="20" customHeight="1">
-      <x:c r="A64" s="143" t="str">
+      <x:c r="A64" s="128" t="str">
         <x:v>FJ-GHRT4B</x:v>
       </x:c>
-      <x:c r="B64" s="147" t="str">
+      <x:c r="B64" s="130" t="str">
         <x:v>כיריים גז 4 מבערים  כפרי שמנת</x:v>
       </x:c>
-      <x:c r="C64" s="153" t="n">
+      <x:c r="C64" s="132" t="str">
+        <x:v>כיריים</x:v>
+      </x:c>
+      <x:c r="D64" s="164" t="n">
         <x:v>620</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="20" customHeight="1">
-      <x:c r="A65" s="143" t="str">
+      <x:c r="A65" s="128" t="str">
         <x:v>FJ-GHRT7CK</x:v>
       </x:c>
-      <x:c r="B65" s="147" t="str">
+      <x:c r="B65" s="130" t="str">
         <x:v>כיריים גז 4 מבערים כפרי  שחור מט</x:v>
       </x:c>
-      <x:c r="C65" s="153" t="n">
+      <x:c r="C65" s="132" t="str">
+        <x:v>כיריים</x:v>
+      </x:c>
+      <x:c r="D65" s="164" t="n">
         <x:v>620</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="20" customHeight="1">
-      <x:c r="A66" s="113" t="str">
+      <x:c r="A66" s="104" t="str">
         <x:v>FJ-HP1010</x:v>
       </x:c>
-      <x:c r="B66" s="117" t="str">
+      <x:c r="B66" s="106" t="str">
         <x:v>מייבש כביסה 10 ק"ג    heat pump</x:v>
       </x:c>
-      <x:c r="C66" s="123" t="n">
+      <x:c r="C66" s="108" t="str">
+        <x:v>מייבשים</x:v>
+      </x:c>
+      <x:c r="D66" s="162" t="n">
         <x:v>1450</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="20" customHeight="1">
-      <x:c r="A67" s="113" t="str">
+      <x:c r="A67" s="104" t="str">
         <x:v>FJ-HP88</x:v>
       </x:c>
-      <x:c r="B67" s="117" t="str">
+      <x:c r="B67" s="106" t="str">
         <x:v>מייבש כביסה 8 ק"ג    heat pump</x:v>
       </x:c>
-      <x:c r="C67" s="123" t="n">
+      <x:c r="C67" s="108" t="str">
+        <x:v>מייבשים</x:v>
+      </x:c>
+      <x:c r="D67" s="162" t="n">
         <x:v>1150</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="20" customHeight="1">
-      <x:c r="A68" s="113" t="str">
+      <x:c r="A68" s="104" t="str">
         <x:v>FJ-HP99</x:v>
       </x:c>
-      <x:c r="B68" s="117" t="str">
+      <x:c r="B68" s="106" t="str">
         <x:v>מייבש כביסה 9 ק"ג    heat pump</x:v>
       </x:c>
-      <x:c r="C68" s="123" t="n">
+      <x:c r="C68" s="108" t="str">
+        <x:v>מייבשים</x:v>
+      </x:c>
+      <x:c r="D68" s="162" t="n">
         <x:v>1250</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="20" customHeight="1">
-      <x:c r="A69" s="143" t="str">
+      <x:c r="A69" s="128" t="str">
         <x:v>FJ-IDZ150</x:v>
       </x:c>
-      <x:c r="B69" s="147" t="str">
+      <x:c r="B69" s="130" t="str">
         <x:v>כיריים אינדוקציה מולטי זון  תלת פאזי שחור</x:v>
       </x:c>
-      <x:c r="C69" s="153" t="n">
+      <x:c r="C69" s="132" t="str">
+        <x:v>כיריים</x:v>
+      </x:c>
+      <x:c r="D69" s="164" t="n">
         <x:v>699</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="20" customHeight="1">
-      <x:c r="A70" s="98" t="str">
+      <x:c r="A70" s="92" t="str">
         <x:v>FJ-KS90BG</x:v>
       </x:c>
-      <x:c r="B70" s="102" t="str">
+      <x:c r="B70" s="94" t="str">
         <x:v>מקרר משרדי 86 ליטר-  דלת זכוכית שחורה</x:v>
       </x:c>
-      <x:c r="C70" s="108" t="n">
+      <x:c r="C70" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D70" s="161" t="n">
         <x:v>475</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="20" customHeight="1">
-      <x:c r="A71" s="98" t="str">
+      <x:c r="A71" s="92" t="str">
         <x:v>FJ-KS93WG</x:v>
       </x:c>
-      <x:c r="B71" s="102" t="str">
+      <x:c r="B71" s="94" t="str">
         <x:v>מקרר משרדי 86 ליטר- דלת זכוכית לבנה</x:v>
       </x:c>
-      <x:c r="C71" s="108" t="n">
+      <x:c r="C71" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D71" s="161" t="n">
         <x:v>475</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="20" customHeight="1">
-      <x:c r="A72" s="53" t="str">
+      <x:c r="A72" s="56" t="str">
         <x:v>FJ-NF241BI</x:v>
       </x:c>
-      <x:c r="B72" s="57" t="str">
+      <x:c r="B72" s="58" t="str">
         <x:v>מקרר  אינטגרלי מקפיא תחתון  NO FROST 248 ליטר</x:v>
       </x:c>
-      <x:c r="C72" s="63" t="n">
+      <x:c r="C72" s="60" t="str">
+        <x:v>קירור אינטגרלי</x:v>
+      </x:c>
+      <x:c r="D72" s="158" t="n">
         <x:v>2190</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="20" customHeight="1">
-      <x:c r="A73" s="98" t="str">
+      <x:c r="A73" s="92" t="str">
         <x:v>FJ-NF295W</x:v>
       </x:c>
-      <x:c r="B73" s="102" t="str">
+      <x:c r="B73" s="94" t="str">
         <x:v>מקרר מקפיא עליון 276 ליטר NF  לבן</x:v>
       </x:c>
-      <x:c r="C73" s="108" t="n">
+      <x:c r="C73" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D73" s="161" t="n">
         <x:v>1090</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="20" customHeight="1">
-      <x:c r="A74" s="53" t="str">
+      <x:c r="A74" s="56" t="str">
         <x:v>FJ-NF304BI</x:v>
       </x:c>
-      <x:c r="B74" s="57" t="str">
+      <x:c r="B74" s="58" t="str">
         <x:v>מקרר אינטגרלי    304 ליטר   NO-FROST</x:v>
       </x:c>
-      <x:c r="C74" s="63" t="n">
+      <x:c r="C74" s="60" t="str">
+        <x:v>קירור אינטגרלי</x:v>
+      </x:c>
+      <x:c r="D74" s="158" t="n">
         <x:v>2190</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="20" customHeight="1">
-      <x:c r="A75" s="98" t="str">
+      <x:c r="A75" s="92" t="str">
         <x:v>FJ-NF323WG</x:v>
       </x:c>
-      <x:c r="B75" s="102" t="str">
+      <x:c r="B75" s="94" t="str">
         <x:v>מקרר מקפיא תחתון 320 ליטר NF - זכוכית לבנה</x:v>
       </x:c>
-      <x:c r="C75" s="108" t="n">
+      <x:c r="C75" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D75" s="161" t="n">
         <x:v>1790</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="20" customHeight="1">
-      <x:c r="A76" s="98" t="str">
+      <x:c r="A76" s="92" t="str">
         <x:v>FJ-NF325BG</x:v>
       </x:c>
-      <x:c r="B76" s="102" t="str">
+      <x:c r="B76" s="94" t="str">
         <x:v>מקרר מקפיא תחתון 320 ליטר NF - זכוכית שחורה</x:v>
       </x:c>
-      <x:c r="C76" s="108" t="n">
+      <x:c r="C76" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D76" s="161" t="n">
         <x:v>1790</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="20" customHeight="1">
-      <x:c r="A77" s="98" t="str">
+      <x:c r="A77" s="92" t="str">
         <x:v>FJ-NF338W</x:v>
       </x:c>
-      <x:c r="B77" s="102" t="str">
+      <x:c r="B77" s="94" t="str">
         <x:v>מקרר מקפיא עליון 329 ליטר לבן</x:v>
       </x:c>
-      <x:c r="C77" s="108" t="n">
+      <x:c r="C77" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D77" s="161" t="n">
         <x:v>1390</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="20" customHeight="1">
-      <x:c r="A78" s="98" t="str">
+      <x:c r="A78" s="92" t="str">
         <x:v>FJ-NF340X</x:v>
       </x:c>
-      <x:c r="B78" s="102" t="str">
+      <x:c r="B78" s="94" t="str">
         <x:v>מקרר מקפיא עליון 329 ליטר NF  נירוסטה</x:v>
       </x:c>
-      <x:c r="C78" s="108" t="n">
+      <x:c r="C78" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D78" s="161" t="n">
         <x:v>1390</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="20" customHeight="1">
-      <x:c r="A79" s="98" t="str">
+      <x:c r="A79" s="92" t="str">
         <x:v>FJ-NF365X</x:v>
       </x:c>
-      <x:c r="B79" s="102" t="str">
+      <x:c r="B79" s="94" t="str">
         <x:v>מקרר מקפיא תחתון 320 ליטר NF -  נירוסטה</x:v>
       </x:c>
-      <x:c r="C79" s="108" t="n">
+      <x:c r="C79" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D79" s="161" t="n">
         <x:v>1690</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="20" customHeight="1">
-      <x:c r="A80" s="53" t="str">
+      <x:c r="A80" s="56" t="str">
         <x:v>FJ-NF3672</x:v>
       </x:c>
-      <x:c r="B80" s="57" t="str">
+      <x:c r="B80" s="58" t="str">
         <x:v>מקרר מקפיא תחתון אינטגרלי 233 ליטר NF</x:v>
       </x:c>
-      <x:c r="C80" s="63" t="n">
+      <x:c r="C80" s="60" t="str">
+        <x:v>קירור אינטגרלי</x:v>
+      </x:c>
+      <x:c r="D80" s="158" t="n">
         <x:v>2290</x:v>
       </x:c>
     </x:row>
     <x:row r="81" ht="20" customHeight="1">
-      <x:c r="A81" s="98" t="str">
+      <x:c r="A81" s="92" t="str">
         <x:v>FJ-NF374DX</x:v>
       </x:c>
-      <x:c r="B81" s="102" t="str">
+      <x:c r="B81" s="94" t="str">
         <x:v>מקרר מקפיא תחתון 320 ליטר NF -  נירוסטה מושחרת</x:v>
       </x:c>
-      <x:c r="C81" s="108" t="n">
+      <x:c r="C81" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D81" s="161" t="n">
         <x:v>1590</x:v>
       </x:c>
     </x:row>
     <x:row r="82" ht="20" customHeight="1">
-      <x:c r="A82" s="98" t="str">
+      <x:c r="A82" s="92" t="str">
         <x:v>FJ-NF394LBM</x:v>
       </x:c>
-      <x:c r="B82" s="102" t="str">
+      <x:c r="B82" s="94" t="str">
         <x:v>מקרר NF  מקפיא תחתון 60ס"מ שחור מט פתיחה לשמאל</x:v>
       </x:c>
-      <x:c r="C82" s="108" t="n">
+      <x:c r="C82" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D82" s="161" t="n">
         <x:v>2200</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="20" customHeight="1">
-      <x:c r="A83" s="98" t="str">
+      <x:c r="A83" s="92" t="str">
         <x:v>FJ-NF423W</x:v>
       </x:c>
-      <x:c r="B83" s="102" t="str">
+      <x:c r="B83" s="94" t="str">
         <x:v>מקרר מקפיא עליון 423 ליטר NO-FROST - לבן</x:v>
       </x:c>
-      <x:c r="C83" s="108" t="n">
+      <x:c r="C83" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D83" s="161" t="n">
         <x:v>1690</x:v>
       </x:c>
     </x:row>
     <x:row r="84" ht="20" customHeight="1">
-      <x:c r="A84" s="98" t="str">
+      <x:c r="A84" s="92" t="str">
         <x:v>FJ-NF433X</x:v>
       </x:c>
-      <x:c r="B84" s="102" t="str">
+      <x:c r="B84" s="94" t="str">
         <x:v>מקרר מקפיא עליון 423 ליטר NO-FROST  נירוסטה</x:v>
       </x:c>
-      <x:c r="C84" s="108" t="n">
+      <x:c r="C84" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D84" s="161" t="n">
         <x:v>1790</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="20" customHeight="1">
-      <x:c r="A85" s="98" t="str">
+      <x:c r="A85" s="92" t="str">
         <x:v>FJ-NF493GBE</x:v>
       </x:c>
-      <x:c r="B85" s="102" t="str">
+      <x:c r="B85" s="94" t="str">
         <x:v>מקרר  מקפיא תחתחון 331 ליטר  זכוכית שחורה</x:v>
       </x:c>
-      <x:c r="C85" s="108" t="n">
+      <x:c r="C85" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D85" s="161" t="n">
         <x:v>2290</x:v>
       </x:c>
     </x:row>
     <x:row r="86" ht="20" customHeight="1">
-      <x:c r="A86" s="98" t="str">
+      <x:c r="A86" s="92" t="str">
         <x:v>FJ-NF500BK</x:v>
       </x:c>
-      <x:c r="B86" s="102" t="str">
+      <x:c r="B86" s="94" t="str">
         <x:v>מקרר 4 דלתות מקפיא תחתון 475 ליטר NO-FROST  זכוכית שחורה</x:v>
       </x:c>
-      <x:c r="C86" s="108" t="n">
+      <x:c r="C86" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D86" s="161" t="n">
         <x:v>2200</x:v>
       </x:c>
     </x:row>
     <x:row r="87" ht="20" customHeight="1">
-      <x:c r="A87" s="98" t="str">
+      <x:c r="A87" s="92" t="str">
         <x:v>FJ-NF513XBF</x:v>
       </x:c>
-      <x:c r="B87" s="102" t="str">
+      <x:c r="B87" s="94" t="str">
         <x:v>מקרר  מקפיא תחתון 499 ליטר NF נירוסטה</x:v>
       </x:c>
-      <x:c r="C87" s="108" t="n">
+      <x:c r="C87" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D87" s="161" t="n">
         <x:v>2590</x:v>
       </x:c>
     </x:row>
     <x:row r="88" ht="20" customHeight="1">
-      <x:c r="A88" s="98" t="str">
+      <x:c r="A88" s="92" t="str">
         <x:v>FJ-NF513XBFIC</x:v>
       </x:c>
-      <x:c r="B88" s="102" t="str">
+      <x:c r="B88" s="94" t="str">
         <x:v>מקרר  מקפיא תחתון 499 ליטר NF נירוסטה + מייצר קרח אוטומטי</x:v>
       </x:c>
-      <x:c r="C88" s="108" t="n">
+      <x:c r="C88" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D88" s="161" t="n">
         <x:v>2790</x:v>
       </x:c>
     </x:row>
     <x:row r="89" ht="20" customHeight="1">
-      <x:c r="A89" s="98" t="str">
+      <x:c r="A89" s="92" t="str">
         <x:v>FJ-NF514DXBF</x:v>
       </x:c>
-      <x:c r="B89" s="102" t="str">
+      <x:c r="B89" s="94" t="str">
         <x:v>מקרר  מקפיא תחתון 499 ליטר NF נירוסטה מושחרת</x:v>
       </x:c>
-      <x:c r="C89" s="108" t="n">
+      <x:c r="C89" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D89" s="161" t="n">
         <x:v>2590</x:v>
       </x:c>
     </x:row>
     <x:row r="90" ht="20" customHeight="1">
-      <x:c r="A90" s="98" t="str">
+      <x:c r="A90" s="92" t="str">
         <x:v>FJ-NF514DXBFIC</x:v>
       </x:c>
-      <x:c r="B90" s="102" t="str">
+      <x:c r="B90" s="94" t="str">
         <x:v>מקרר  מקפיא תחתון 499 ליטר NF נירוסטה מושחרת+מייצר קרח אוט'</x:v>
       </x:c>
-      <x:c r="C90" s="108" t="n">
+      <x:c r="C90" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D90" s="161" t="n">
         <x:v>2790</x:v>
       </x:c>
     </x:row>
     <x:row r="91" ht="20" customHeight="1">
-      <x:c r="A91" s="98" t="str">
+      <x:c r="A91" s="92" t="str">
         <x:v>FJ-NF515W</x:v>
       </x:c>
-      <x:c r="B91" s="102" t="str">
+      <x:c r="B91" s="94" t="str">
         <x:v>מקרר 4 דלתות מקפיא תחתון 475 ליטר NO-FROST  זכוכית לבנה</x:v>
       </x:c>
-      <x:c r="C91" s="108" t="n">
+      <x:c r="C91" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D91" s="161" t="n">
         <x:v>2350</x:v>
       </x:c>
     </x:row>
     <x:row r="92" ht="20" customHeight="1">
-      <x:c r="A92" s="98" t="str">
+      <x:c r="A92" s="92" t="str">
         <x:v>FJ-NF516WBF</x:v>
       </x:c>
-      <x:c r="B92" s="102" t="str">
+      <x:c r="B92" s="94" t="str">
         <x:v>מקרר  מקפיא תחתון 499 ליטר NF לבן</x:v>
       </x:c>
-      <x:c r="C92" s="108" t="n">
+      <x:c r="C92" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D92" s="161" t="n">
         <x:v>2590</x:v>
       </x:c>
     </x:row>
     <x:row r="93" ht="20" customHeight="1">
-      <x:c r="A93" s="98" t="str">
+      <x:c r="A93" s="92" t="str">
         <x:v>FJ-NF516WBFIC</x:v>
       </x:c>
-      <x:c r="B93" s="102" t="str">
+      <x:c r="B93" s="94" t="str">
         <x:v>מקרר  מקפיא תחתון 499 ליטר NF לבן + מייצר קרח אוטומטי</x:v>
       </x:c>
-      <x:c r="C93" s="108" t="n">
+      <x:c r="C93" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D93" s="161" t="n">
         <x:v>2790</x:v>
       </x:c>
     </x:row>
     <x:row r="94" ht="20" customHeight="1">
-      <x:c r="A94" s="98" t="str">
+      <x:c r="A94" s="92" t="str">
         <x:v>FJ-NF530GDBL</x:v>
       </x:c>
-      <x:c r="B94" s="102" t="str">
+      <x:c r="B94" s="94" t="str">
         <x:v>מקרר 4 דלתות 505 ליטר NF  זכוכית שחורה</x:v>
       </x:c>
-      <x:c r="C94" s="108" t="n">
+      <x:c r="C94" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D94" s="161" t="n">
         <x:v>3290</x:v>
       </x:c>
     </x:row>
     <x:row r="95" ht="20" customHeight="1">
-      <x:c r="A95" s="98" t="str">
+      <x:c r="A95" s="92" t="str">
         <x:v>FJ-NF549W</x:v>
       </x:c>
-      <x:c r="B95" s="102" t="str">
+      <x:c r="B95" s="94" t="str">
         <x:v>מקרר מקפיא עליון 401 ליטר NF לבן</x:v>
       </x:c>
-      <x:c r="C95" s="108" t="n">
+      <x:c r="C95" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D95" s="161" t="n">
         <x:v>1690</x:v>
       </x:c>
     </x:row>
     <x:row r="96" ht="20" customHeight="1">
-      <x:c r="A96" s="98" t="str">
+      <x:c r="A96" s="92" t="str">
         <x:v>FJ-NF560DX</x:v>
       </x:c>
-      <x:c r="B96" s="102" t="str">
+      <x:c r="B96" s="94" t="str">
         <x:v>מקרר 4 דלתות 505 ליטר NF  נירוסטה מושחרת</x:v>
       </x:c>
-      <x:c r="C96" s="108" t="n">
+      <x:c r="C96" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D96" s="161" t="n">
         <x:v>3090</x:v>
       </x:c>
     </x:row>
     <x:row r="97" ht="20" customHeight="1">
-      <x:c r="A97" s="98" t="str">
+      <x:c r="A97" s="92" t="str">
         <x:v>FJ-NF590GDW</x:v>
       </x:c>
-      <x:c r="B97" s="102" t="str">
+      <x:c r="B97" s="94" t="str">
         <x:v>מקרר 4 דלתות 505 ליטר NF  זכוכית לבנה</x:v>
       </x:c>
-      <x:c r="C97" s="108" t="n">
+      <x:c r="C97" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D97" s="161" t="n">
         <x:v>3290</x:v>
       </x:c>
     </x:row>
     <x:row r="98" ht="20" customHeight="1">
-      <x:c r="A98" s="98" t="str">
+      <x:c r="A98" s="92" t="str">
         <x:v>FJ-NF600BK</x:v>
       </x:c>
-      <x:c r="B98" s="102" t="str">
+      <x:c r="B98" s="94" t="str">
         <x:v>מקרר 4 דלתות מקפיא תחתון 539 ליטר NO-FROST זכוכית שחורה</x:v>
       </x:c>
-      <x:c r="C98" s="108" t="n">
+      <x:c r="C98" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D98" s="161" t="n">
         <x:v>2490</x:v>
       </x:c>
     </x:row>
     <x:row r="99" ht="20" customHeight="1">
-      <x:c r="A99" s="98" t="str">
+      <x:c r="A99" s="92" t="str">
         <x:v>FJ-NF615W</x:v>
       </x:c>
-      <x:c r="B99" s="102" t="str">
+      <x:c r="B99" s="94" t="str">
         <x:v>מקרר 4 דלתות מקפיא תחתון 539 ליטר NO-FROST זכוכית לבנה</x:v>
       </x:c>
-      <x:c r="C99" s="108" t="n">
+      <x:c r="C99" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D99" s="161" t="n">
         <x:v>2490</x:v>
       </x:c>
     </x:row>
     <x:row r="100" ht="20" customHeight="1">
-      <x:c r="A100" s="98" t="str">
+      <x:c r="A100" s="92" t="str">
         <x:v>FJ-NF645W</x:v>
       </x:c>
-      <x:c r="B100" s="102" t="str">
+      <x:c r="B100" s="94" t="str">
         <x:v>מקרר מקפיא עליון  497 ליטר NF -  לבן</x:v>
       </x:c>
-      <x:c r="C100" s="108" t="n">
+      <x:c r="C100" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D100" s="161" t="n">
         <x:v>1890</x:v>
       </x:c>
     </x:row>
     <x:row r="101" ht="20" customHeight="1">
-      <x:c r="A101" s="98" t="str">
+      <x:c r="A101" s="92" t="str">
         <x:v>FJ-NF655BGE</x:v>
       </x:c>
-      <x:c r="B101" s="102" t="str">
+      <x:c r="B101" s="94" t="str">
         <x:v>מקרר מקפיא תחתון 588 ליטר NO-FROST שמנת</x:v>
       </x:c>
-      <x:c r="C101" s="108" t="n">
+      <x:c r="C101" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D101" s="161" t="n">
         <x:v>2890</x:v>
       </x:c>
     </x:row>
     <x:row r="102" ht="20" customHeight="1">
-      <x:c r="A102" s="98" t="str">
+      <x:c r="A102" s="92" t="str">
         <x:v>FJ-NF676LBM</x:v>
       </x:c>
-      <x:c r="B102" s="102" t="str">
+      <x:c r="B102" s="94" t="str">
         <x:v>מקרר  מקפיא תחתון 331 ליטר NF שחור מט (פתיחה הפוכה)</x:v>
       </x:c>
-      <x:c r="C102" s="108" t="n">
+      <x:c r="C102" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D102" s="161" t="n">
         <x:v>2290</x:v>
       </x:c>
     </x:row>
     <x:row r="103" ht="20" customHeight="1">
-      <x:c r="A103" s="98" t="str">
+      <x:c r="A103" s="92" t="str">
         <x:v>FJ-NF681W</x:v>
       </x:c>
-      <x:c r="B103" s="102" t="str">
+      <x:c r="B103" s="94" t="str">
         <x:v>מקרר מקפיא תחתון  NO-FROST 680 ליטר לבן</x:v>
       </x:c>
-      <x:c r="C103" s="108" t="n">
+      <x:c r="C103" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D103" s="161" t="n">
         <x:v>2890</x:v>
       </x:c>
     </x:row>
     <x:row r="104" ht="20" customHeight="1">
-      <x:c r="A104" s="98" t="str">
+      <x:c r="A104" s="92" t="str">
         <x:v>FJ-NF682X</x:v>
       </x:c>
-      <x:c r="B104" s="102" t="str">
+      <x:c r="B104" s="94" t="str">
         <x:v>מקרר מקפיא תחתון  NO-FROST 680 ליטר נירוסטה</x:v>
       </x:c>
-      <x:c r="C104" s="108" t="n">
+      <x:c r="C104" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D104" s="161" t="n">
         <x:v>2890</x:v>
       </x:c>
     </x:row>
     <x:row r="105" ht="20" customHeight="1">
-      <x:c r="A105" s="98" t="str">
+      <x:c r="A105" s="92" t="str">
         <x:v>FJ-NF683DX</x:v>
       </x:c>
-      <x:c r="B105" s="102" t="str">
+      <x:c r="B105" s="94" t="str">
         <x:v>מקרר מקפיא תחתון  NO-FROST 680 ליטר נירוסטה מושחרת</x:v>
       </x:c>
-      <x:c r="C105" s="108" t="n">
+      <x:c r="C105" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D105" s="161" t="n">
         <x:v>2890</x:v>
       </x:c>
     </x:row>
     <x:row r="106" ht="20" customHeight="1">
-      <x:c r="A106" s="98" t="str">
+      <x:c r="A106" s="92" t="str">
         <x:v>FJ-NF696RBM</x:v>
       </x:c>
-      <x:c r="B106" s="102" t="str">
+      <x:c r="B106" s="94" t="str">
         <x:v>מקרר  מקפיא תחתון 331 ליטר NF שחור מט (פתיחה רגילה )</x:v>
       </x:c>
-      <x:c r="C106" s="108" t="n">
+      <x:c r="C106" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D106" s="161" t="n">
         <x:v>2290</x:v>
       </x:c>
     </x:row>
     <x:row r="107" ht="20" customHeight="1">
-      <x:c r="A107" s="98" t="str">
+      <x:c r="A107" s="92" t="str">
         <x:v>FJ-NF70X</x:v>
       </x:c>
-      <x:c r="B107" s="102" t="str">
+      <x:c r="B107" s="94" t="str">
         <x:v>מקרר מקפיא תחתון 435 ליטר NO  FROST  נירוסטה</x:v>
       </x:c>
-      <x:c r="C107" s="108" t="n">
+      <x:c r="C107" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D107" s="161" t="n">
         <x:v>2190</x:v>
       </x:c>
     </x:row>
     <x:row r="108" ht="20" customHeight="1">
-      <x:c r="A108" s="98" t="str">
+      <x:c r="A108" s="92" t="str">
         <x:v>FJ-NF745DX</x:v>
       </x:c>
-      <x:c r="B108" s="102" t="str">
+      <x:c r="B108" s="94" t="str">
         <x:v>מקרר מקפיא עליון 497 ליטר NF -  נירוסטה מושחרת</x:v>
       </x:c>
-      <x:c r="C108" s="108" t="n">
+      <x:c r="C108" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D108" s="161" t="n">
         <x:v>1990</x:v>
       </x:c>
     </x:row>
     <x:row r="109" ht="20" customHeight="1">
-      <x:c r="A109" s="98" t="str">
+      <x:c r="A109" s="92" t="str">
         <x:v>FJ-NF766WE</x:v>
       </x:c>
-      <x:c r="B109" s="102" t="str">
+      <x:c r="B109" s="94" t="str">
         <x:v>מקרר מקפיא תחתון 588 ליטר NO-FROST לבן</x:v>
       </x:c>
-      <x:c r="C109" s="108" t="n">
+      <x:c r="C109" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D109" s="161" t="n">
         <x:v>2890</x:v>
       </x:c>
     </x:row>
     <x:row r="110" ht="20" customHeight="1">
-      <x:c r="A110" s="98" t="str">
+      <x:c r="A110" s="92" t="str">
         <x:v>FJ-NF777XE</x:v>
       </x:c>
-      <x:c r="B110" s="102" t="str">
+      <x:c r="B110" s="94" t="str">
         <x:v>מקרר מקפיא תחתון 588 ליטר NO-FROST נירוסטה</x:v>
       </x:c>
-      <x:c r="C110" s="108" t="n">
+      <x:c r="C110" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D110" s="161" t="n">
         <x:v>2890</x:v>
       </x:c>
     </x:row>
     <x:row r="111" ht="20" customHeight="1">
-      <x:c r="A111" s="98" t="str">
+      <x:c r="A111" s="92" t="str">
         <x:v>FJ-NF800BK</x:v>
       </x:c>
-      <x:c r="B111" s="102" t="str">
+      <x:c r="B111" s="94" t="str">
         <x:v>מקרר 4 דלתות מקפיא תחתון 600 ליטר NO-FROST זכוכית שחורה</x:v>
       </x:c>
-      <x:c r="C111" s="108" t="n">
+      <x:c r="C111" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D111" s="161" t="n">
         <x:v>3800</x:v>
       </x:c>
     </x:row>
     <x:row r="112" ht="20" customHeight="1">
-      <x:c r="A112" s="98" t="str">
+      <x:c r="A112" s="92" t="str">
         <x:v>FJ-NF815W</x:v>
       </x:c>
-      <x:c r="B112" s="102" t="str">
+      <x:c r="B112" s="94" t="str">
         <x:v>מקרר 4 דלתות מקפיא תחתון 600 ליטר NO-FROST זכוכית לבנה</x:v>
       </x:c>
-      <x:c r="C112" s="108" t="n">
+      <x:c r="C112" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D112" s="161" t="n">
         <x:v>3800</x:v>
       </x:c>
     </x:row>
     <x:row r="113" ht="20" customHeight="1">
-      <x:c r="A113" s="98" t="str">
+      <x:c r="A113" s="92" t="str">
         <x:v>FJ-NF820DX</x:v>
       </x:c>
-      <x:c r="B113" s="102" t="str">
+      <x:c r="B113" s="94" t="str">
         <x:v>מקרר NO FROST  4 דלתות 600 ליטר נירוסטה מושחרת  FJ-NF820DX</x:v>
       </x:c>
-      <x:c r="C113" s="108" t="n">
+      <x:c r="C113" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D113" s="161" t="n">
         <x:v>3800</x:v>
       </x:c>
     </x:row>
     <x:row r="114" ht="20" customHeight="1">
-      <x:c r="A114" s="98" t="str">
+      <x:c r="A114" s="92" t="str">
         <x:v>FJ-NF836DXE</x:v>
       </x:c>
-      <x:c r="B114" s="102" t="str">
+      <x:c r="B114" s="94" t="str">
         <x:v>מקרר מקפיא תחתון 588 ליטר NO-FROST נירוסטה מושחרת</x:v>
       </x:c>
-      <x:c r="C114" s="108" t="n">
+      <x:c r="C114" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D114" s="161" t="n">
         <x:v>2890</x:v>
       </x:c>
     </x:row>
     <x:row r="115" ht="20" customHeight="1">
-      <x:c r="A115" s="98" t="str">
+      <x:c r="A115" s="92" t="str">
         <x:v>FJ-NF838RDXE</x:v>
       </x:c>
-      <x:c r="B115" s="102" t="str">
+      <x:c r="B115" s="94" t="str">
         <x:v>מקרר מקפיא תחתון 331 ליטר NF נירוסטה מושחרת ( פתיחה רגילה)</x:v>
       </x:c>
-      <x:c r="C115" s="108" t="n">
+      <x:c r="C115" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D115" s="161" t="n">
         <x:v>1990</x:v>
       </x:c>
     </x:row>
     <x:row r="116" ht="20" customHeight="1">
-      <x:c r="A116" s="98" t="str">
+      <x:c r="A116" s="92" t="str">
         <x:v>FJ-NF888BME</x:v>
       </x:c>
-      <x:c r="B116" s="102" t="str">
+      <x:c r="B116" s="94" t="str">
         <x:v>מקרר מקפיא תחתון  588 ליטר NO-FROST שחור מט</x:v>
       </x:c>
-      <x:c r="C116" s="108" t="n">
+      <x:c r="C116" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D116" s="161" t="n">
         <x:v>2890</x:v>
       </x:c>
     </x:row>
     <x:row r="117" ht="20" customHeight="1">
-      <x:c r="A117" s="98" t="str">
+      <x:c r="A117" s="92" t="str">
         <x:v>FJ-NF949RXE</x:v>
       </x:c>
-      <x:c r="B117" s="102" t="str">
+      <x:c r="B117" s="94" t="str">
         <x:v>מקרר  מקפיא תחתון 331 ליטר NF נירוסטה (פתיחה רגילה )</x:v>
       </x:c>
-      <x:c r="C117" s="108" t="n">
+      <x:c r="C117" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D117" s="161" t="n">
         <x:v>1990</x:v>
       </x:c>
     </x:row>
     <x:row r="118" ht="20" customHeight="1">
-      <x:c r="A118" s="98" t="str">
+      <x:c r="A118" s="92" t="str">
         <x:v>FJ-NFRT325BK</x:v>
       </x:c>
-      <x:c r="B118" s="102" t="str">
+      <x:c r="B118" s="94" t="str">
         <x:v>מקרר NF  רטרו  שחור  FJ-NFRT325BK  310L</x:v>
       </x:c>
-      <x:c r="C118" s="108" t="n">
+      <x:c r="C118" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D118" s="161" t="n">
         <x:v>1790</x:v>
       </x:c>
     </x:row>
     <x:row r="119" ht="20" customHeight="1">
-      <x:c r="A119" s="98" t="str">
+      <x:c r="A119" s="92" t="str">
         <x:v>FJ-V107TE</x:v>
       </x:c>
-      <x:c r="B119" s="102" t="str">
+      <x:c r="B119" s="94" t="str">
         <x:v>מקרר משרדי DF  ויטרינה מסחרי 93 ליטר</x:v>
       </x:c>
-      <x:c r="C119" s="108" t="n">
+      <x:c r="C119" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D119" s="161" t="n">
         <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="120" ht="20" customHeight="1">
-      <x:c r="A120" s="98" t="str">
+      <x:c r="A120" s="92" t="str">
         <x:v>FJ-V375</x:v>
       </x:c>
-      <x:c r="B120" s="102" t="str">
+      <x:c r="B120" s="94" t="str">
         <x:v>מקרר ויטרינה מסחרי 350 ליטר</x:v>
       </x:c>
-      <x:c r="C120" s="108" t="n">
+      <x:c r="C120" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D120" s="161" t="n">
         <x:v>1450</x:v>
       </x:c>
     </x:row>
     <x:row r="121" ht="20" customHeight="1">
-      <x:c r="A121" s="98" t="str">
+      <x:c r="A121" s="92" t="str">
         <x:v>FJ-V65TE</x:v>
       </x:c>
-      <x:c r="B121" s="102" t="str">
+      <x:c r="B121" s="94" t="str">
         <x:v>מקרר קוביה DF ויטרינה מסחרי 46 ליטר</x:v>
       </x:c>
-      <x:c r="C121" s="108" t="n">
+      <x:c r="C121" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D121" s="161" t="n">
         <x:v>400</x:v>
       </x:c>
     </x:row>
     <x:row r="122" ht="20" customHeight="1">
-      <x:c r="A122" s="98" t="str">
+      <x:c r="A122" s="92" t="str">
         <x:v>FJ-WC118</x:v>
       </x:c>
-      <x:c r="B122" s="102" t="str">
+      <x:c r="B122" s="94" t="str">
         <x:v>מקרר יין 116 ל'  49 בקבוקים מדפי עץ</x:v>
       </x:c>
-      <x:c r="C122" s="108" t="n">
+      <x:c r="C122" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D122" s="161" t="n">
         <x:v>990</x:v>
       </x:c>
     </x:row>
     <x:row r="123" ht="20" customHeight="1">
-      <x:c r="A123" s="158" t="str">
+      <x:c r="A123" s="140" t="str">
         <x:v>FJ-WM1014W</x:v>
       </x:c>
-      <x:c r="B123" s="162" t="str">
+      <x:c r="B123" s="142" t="str">
         <x:v>מכונת כביסה 10 ק"ג 1400 סל"ד אינוורטר</x:v>
       </x:c>
-      <x:c r="C123" s="168" t="n">
+      <x:c r="C123" s="144" t="str">
+        <x:v>מכונות כביסה</x:v>
+      </x:c>
+      <x:c r="D123" s="165" t="n">
         <x:v>1290</x:v>
       </x:c>
     </x:row>
     <x:row r="124" ht="20" customHeight="1">
-      <x:c r="A124" s="158" t="str">
+      <x:c r="A124" s="140" t="str">
         <x:v>FJ-WM1215W</x:v>
       </x:c>
-      <x:c r="B124" s="162" t="str">
+      <x:c r="B124" s="142" t="str">
         <x:v>מכונת כביסה  12 ק"ג  1400 סל"ד</x:v>
       </x:c>
-      <x:c r="C124" s="168" t="n">
+      <x:c r="C124" s="144" t="str">
+        <x:v>מכונות כביסה</x:v>
+      </x:c>
+      <x:c r="D124" s="165" t="n">
         <x:v>1250</x:v>
       </x:c>
     </x:row>
     <x:row r="125" ht="20" customHeight="1">
-      <x:c r="A125" s="158" t="str">
+      <x:c r="A125" s="140" t="str">
         <x:v>FJ-WM69</x:v>
       </x:c>
-      <x:c r="B125" s="162" t="str">
+      <x:c r="B125" s="142" t="str">
         <x:v>מכונת כביסה 6 ק"ג 1000 סל"ד</x:v>
       </x:c>
-      <x:c r="C125" s="168" t="n">
+      <x:c r="C125" s="144" t="str">
+        <x:v>מכונות כביסה</x:v>
+      </x:c>
+      <x:c r="D125" s="165" t="n">
         <x:v>690</x:v>
       </x:c>
     </x:row>
     <x:row r="126" ht="20" customHeight="1">
-      <x:c r="A126" s="158" t="str">
+      <x:c r="A126" s="140" t="str">
         <x:v>FJ-WM72</x:v>
       </x:c>
-      <x:c r="B126" s="162" t="str">
+      <x:c r="B126" s="142" t="str">
         <x:v>מכונת כביסה 7 ק"ג  1200 סל"ד INVERTER</x:v>
       </x:c>
-      <x:c r="C126" s="168" t="n">
+      <x:c r="C126" s="144" t="str">
+        <x:v>מכונות כביסה</x:v>
+      </x:c>
+      <x:c r="D126" s="165" t="n">
         <x:v>790</x:v>
       </x:c>
     </x:row>
     <x:row r="127" ht="20" customHeight="1">
-      <x:c r="A127" s="158" t="str">
+      <x:c r="A127" s="140" t="str">
         <x:v>FJ-WM86</x:v>
       </x:c>
-      <x:c r="B127" s="162" t="str">
+      <x:c r="B127" s="142" t="str">
         <x:v>מכונת כביסה 8 ק"ג  1400 סל"ד INVERTER</x:v>
       </x:c>
-      <x:c r="C127" s="168" t="n">
+      <x:c r="C127" s="144" t="str">
+        <x:v>מכונות כביסה</x:v>
+      </x:c>
+      <x:c r="D127" s="165" t="n">
         <x:v>890</x:v>
       </x:c>
     </x:row>
     <x:row r="128" ht="20" customHeight="1">
-      <x:c r="A128" s="158" t="str">
+      <x:c r="A128" s="140" t="str">
         <x:v>FJ-WM912W</x:v>
       </x:c>
-      <x:c r="B128" s="162" t="str">
+      <x:c r="B128" s="142" t="str">
         <x:v>מכונת כביסה 9 ק"ג 1200 סל"ד INVERTER</x:v>
       </x:c>
-      <x:c r="C128" s="168" t="n">
+      <x:c r="C128" s="144" t="str">
+        <x:v>מכונות כביסה</x:v>
+      </x:c>
+      <x:c r="D128" s="165" t="n">
         <x:v>990</x:v>
       </x:c>
     </x:row>
     <x:row r="129" ht="20" customHeight="1">
-      <x:c r="A129" s="98" t="str">
+      <x:c r="A129" s="92" t="str">
         <x:v>IT-170L</x:v>
       </x:c>
-      <x:c r="B129" s="102" t="str">
+      <x:c r="B129" s="94" t="str">
         <x:v>מקרר מקפיא תחתון  170 ליטר  DE-FROST  לבן</x:v>
       </x:c>
-      <x:c r="C129" s="108" t="n">
+      <x:c r="C129" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D129" s="161" t="n">
         <x:v>550</x:v>
       </x:c>
     </x:row>
     <x:row r="130" ht="20" customHeight="1">
-      <x:c r="A130" s="98" t="str">
+      <x:c r="A130" s="92" t="str">
         <x:v>IT-CF244</x:v>
       </x:c>
-      <x:c r="B130" s="102" t="str">
+      <x:c r="B130" s="94" t="str">
         <x:v>מקפיא  מסחרי שוכב 244 ליטר DE-FROST לבן</x:v>
       </x:c>
-      <x:c r="C130" s="108" t="n">
+      <x:c r="C130" s="96" t="str">
+        <x:v>מקררים ומקפיאים</x:v>
+      </x:c>
+      <x:c r="D130" s="161" t="n">
         <x:v>690</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:C1"/>
+    <x:mergeCell ref="A1:D1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra0e5e29a8f43494e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb5856a6983364207"/>
   </x:tableParts>
 </x:worksheet>
 </file>